--- a/result_sentiment_adjusted_Q/evaluation_metrics.xlsx
+++ b/result_sentiment_adjusted_Q/evaluation_metrics.xlsx
@@ -462,19 +462,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1807271478657778</v>
+        <v>0.1807271344036079</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4331297641649495</v>
+        <v>0.4331300178292418</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2201006090695642</v>
+        <v>0.2201005012310898</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2392681630875157</v>
+        <v>0.2392680792094109</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2352874954234846</v>
+        <v>0.2352873825885871</v>
       </c>
     </row>
     <row r="3">
@@ -484,19 +484,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.076066801635659</v>
+        <v>1.076066752993368</v>
       </c>
       <c r="C3" t="n">
-        <v>1.250937383555045</v>
+        <v>1.250937387120761</v>
       </c>
       <c r="D3" t="n">
-        <v>1.154997721214607</v>
+        <v>1.154997036985717</v>
       </c>
       <c r="E3" t="n">
-        <v>1.17662592471081</v>
+        <v>1.176625388335971</v>
       </c>
       <c r="F3" t="n">
-        <v>1.04473045856158</v>
+        <v>1.044729702475751</v>
       </c>
     </row>
     <row r="4">
@@ -507,16 +507,16 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>0.9907961520827926</v>
+        <v>0.9907966282521912</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6678553553058925</v>
+        <v>0.6678530320145066</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7172839681007758</v>
+        <v>0.7172828369038098</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4845528068031085</v>
+        <v>0.4845517329248966</v>
       </c>
     </row>
     <row r="5">
@@ -526,19 +526,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.2028774444126785</v>
+        <v>-0.2028773863168427</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.4525305271753218</v>
+        <v>-0.452530631002677</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2780680101335716</v>
+        <v>-0.2780680754738878</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3089628114466361</v>
+        <v>-0.3089628860330432</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3553680663724877</v>
+        <v>-0.3553682997090751</v>
       </c>
     </row>
     <row r="6">
@@ -548,19 +548,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1679516063417868</v>
+        <v>0.167951601423301</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3462441604663185</v>
+        <v>0.3462443622587396</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1905636738729703</v>
+        <v>0.190563693397433</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2033510889591548</v>
+        <v>0.2033511103714947</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2252135883426205</v>
+        <v>0.225213643329001</v>
       </c>
     </row>
     <row r="7">
@@ -570,19 +570,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.07370892045712596</v>
+        <v>-0.0737089452488867</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.1207385225840497</v>
+        <v>-0.1207384822071983</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.08182220133997387</v>
+        <v>-0.08182216831353969</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.08710518554249072</v>
+        <v>-0.08710519545995069</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.09738177952732877</v>
+        <v>-0.09738185072464102</v>
       </c>
     </row>
     <row r="8">
@@ -595,16 +595,16 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6380535492362425</v>
+        <v>0.6380535544738818</v>
       </c>
       <c r="D8" t="n">
-        <v>0.06139293521369462</v>
+        <v>0.06139300902410207</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1572396039177015</v>
+        <v>0.1572399172977312</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3767783587608393</v>
+        <v>0.3767784543333612</v>
       </c>
     </row>
   </sheetData>

--- a/result_sentiment_adjusted_Q/evaluation_metrics.xlsx
+++ b/result_sentiment_adjusted_Q/evaluation_metrics.xlsx
@@ -441,17 +441,17 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Sentiment BL (Baseline Omega)</t>
+          <t>RAW Sentiment BL (Baseline Omega)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Sentiment BL (Advanced Omega)</t>
+          <t>RAW Sentiment BL (Advanced Omega)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Sentiment Dynamic BL</t>
+          <t>RAW Sentiment Dynamic BL</t>
         </is>
       </c>
     </row>
@@ -462,19 +462,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1807271344036079</v>
+        <v>0.1807271374065327</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4331300178292418</v>
+        <v>0.4331299891482575</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2201005012310898</v>
+        <v>0.2201005070173749</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2392680792094109</v>
+        <v>0.2392681540663875</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2352873825885871</v>
+        <v>0.2352874789007391</v>
       </c>
     </row>
     <row r="3">
@@ -484,19 +484,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.076066752993368</v>
+        <v>1.076066663596196</v>
       </c>
       <c r="C3" t="n">
-        <v>1.250937387120761</v>
+        <v>1.250937268983203</v>
       </c>
       <c r="D3" t="n">
-        <v>1.154997036985717</v>
+        <v>1.154997069518551</v>
       </c>
       <c r="E3" t="n">
-        <v>1.176625388335971</v>
+        <v>1.176625662700239</v>
       </c>
       <c r="F3" t="n">
-        <v>1.044729702475751</v>
+        <v>1.044729925675667</v>
       </c>
     </row>
     <row r="4">
@@ -507,16 +507,16 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>0.9907966282521912</v>
+        <v>0.9907964388844448</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6678530320145066</v>
+        <v>0.6678531353588788</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7172828369038098</v>
+        <v>0.7172838556096787</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4845517329248966</v>
+        <v>0.4845525786168947</v>
       </c>
     </row>
     <row r="5">
@@ -526,19 +526,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.2028773863168427</v>
+        <v>-0.2028774508884138</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.452530631002677</v>
+        <v>-0.4525306064401637</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2780680754738878</v>
+        <v>-0.2780681999688465</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3089628860330432</v>
+        <v>-0.3089628874726069</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3553682997090751</v>
+        <v>-0.3553683785948052</v>
       </c>
     </row>
     <row r="6">
@@ -548,19 +548,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.167951601423301</v>
+        <v>0.1679516181669876</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3462443622587396</v>
+        <v>0.3462443720301961</v>
       </c>
       <c r="D6" t="n">
-        <v>0.190563693397433</v>
+        <v>0.1905636930396036</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2033511103714947</v>
+        <v>0.2033511265743524</v>
       </c>
       <c r="F6" t="n">
-        <v>0.225213643329001</v>
+        <v>0.2252136874021003</v>
       </c>
     </row>
     <row r="7">
@@ -570,19 +570,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.0737089452488867</v>
+        <v>-0.07370896689482442</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.1207384822071983</v>
+        <v>-0.1207385826560214</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.08182216831353969</v>
+        <v>-0.08182223506434683</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.08710519545995069</v>
+        <v>-0.08710519410966466</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.09738185072464102</v>
+        <v>-0.09738182847686389</v>
       </c>
     </row>
     <row r="8">
@@ -595,16 +595,16 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6380535544738818</v>
+        <v>0.6380536831046097</v>
       </c>
       <c r="D8" t="n">
-        <v>0.06139300902410207</v>
+        <v>0.06139298543065741</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1572399172977312</v>
+        <v>0.1572397642942774</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3767784543333612</v>
+        <v>0.3767782789755982</v>
       </c>
     </row>
   </sheetData>

--- a/result_sentiment_adjusted_Q/evaluation_metrics.xlsx
+++ b/result_sentiment_adjusted_Q/evaluation_metrics.xlsx
@@ -462,19 +462,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1807271374065327</v>
+        <v>0.1710126995111861</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4331299891482575</v>
+        <v>0.4049178582871612</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2201005070173749</v>
+        <v>0.1939703894627932</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2392681540663875</v>
+        <v>0.214624140535691</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2352874789007391</v>
+        <v>0.2193739831441971</v>
       </c>
     </row>
     <row r="3">
@@ -484,19 +484,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.076066663596196</v>
+        <v>1.144890112258371</v>
       </c>
       <c r="C3" t="n">
-        <v>1.250937268983203</v>
+        <v>1.160894442697566</v>
       </c>
       <c r="D3" t="n">
-        <v>1.154997069518551</v>
+        <v>1.080989801407628</v>
       </c>
       <c r="E3" t="n">
-        <v>1.176625662700239</v>
+        <v>1.132898509608024</v>
       </c>
       <c r="F3" t="n">
-        <v>1.044729925675667</v>
+        <v>1.126472658581236</v>
       </c>
     </row>
     <row r="4">
@@ -507,16 +507,16 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>0.9907964388844448</v>
+        <v>0.8936043986040845</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6678531353588788</v>
+        <v>0.414883048441232</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7172838556096787</v>
+        <v>0.5996862667152726</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4845525786168947</v>
+        <v>0.5399633801994974</v>
       </c>
     </row>
     <row r="5">
@@ -526,19 +526,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.2028774508884138</v>
+        <v>-0.2028774012753196</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.4525306064401637</v>
+        <v>-0.4525305106667451</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2780681999688465</v>
+        <v>-0.2715310900557988</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3089628874726069</v>
+        <v>-0.2984331714520753</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3553683785948052</v>
+        <v>-0.2753185598698785</v>
       </c>
     </row>
     <row r="6">
@@ -548,19 +548,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1679516181669876</v>
+        <v>0.1493704047926943</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3462443720301961</v>
+        <v>0.3487981709570898</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1905636930396036</v>
+        <v>0.1794377608467828</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2033511265743524</v>
+        <v>0.1894469263711449</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2252136874021003</v>
+        <v>0.1947441701962772</v>
       </c>
     </row>
     <row r="7">
@@ -570,19 +570,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.07370896689482442</v>
+        <v>-0.05269718626937447</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.1207385826560214</v>
+        <v>-0.1272865239573453</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.08182223506434683</v>
+        <v>-0.0628198079366271</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.08710519410966466</v>
+        <v>-0.07467974982778716</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.09738182847686389</v>
+        <v>-0.08837081905292817</v>
       </c>
     </row>
     <row r="8">
@@ -595,16 +595,16 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6380536831046097</v>
+        <v>0.710015972005132</v>
       </c>
       <c r="D8" t="n">
-        <v>0.06139298543065741</v>
+        <v>0.08432804632459089</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1572397642942774</v>
+        <v>0.1561427992380214</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3767782789755982</v>
+        <v>0.3434836760998189</v>
       </c>
     </row>
   </sheetData>

--- a/result_sentiment_adjusted_Q/evaluation_metrics.xlsx
+++ b/result_sentiment_adjusted_Q/evaluation_metrics.xlsx
@@ -1,37 +1,85 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chenyu/Desktop/ORIE 5370 Optimization for Finance/Dynamic-Black-Litterman-Portfolio-Construction/result_sentiment_adjusted_Q/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CA193E2-3548-4C4A-A5D0-5F014CD55C14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="30240" windowHeight="19640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+  <si>
+    <t>Equal Weight (1/N)</t>
+  </si>
+  <si>
+    <t>Benchmark 1 (MVO)</t>
+  </si>
+  <si>
+    <t>Sentiment BL (Baseline Omega)</t>
+  </si>
+  <si>
+    <t>Sentiment BL (Advanced Omega)</t>
+  </si>
+  <si>
+    <t>Sentiment Dynamic BL</t>
+  </si>
+  <si>
+    <t>Annualized Return</t>
+  </si>
+  <si>
+    <t>Sharpe Ratio</t>
+  </si>
+  <si>
+    <t>Information Ratio</t>
+  </si>
+  <si>
+    <t>Maximum Drawdown</t>
+  </si>
+  <si>
+    <t>Annualized Volatility</t>
+  </si>
+  <si>
+    <t>Value at Risk (95%)</t>
+  </si>
+  <si>
+    <t>Annualized Turnover</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +94,43 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,191 +418,169 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Equal Weight (1/N)</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Benchmark 1 (MVO)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>RAW Sentiment BL (Baseline Omega)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>RAW Sentiment BL (Advanced Omega)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>RAW Sentiment Dynamic BL</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Annualized Return</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0.1710126995111861</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.4049178582871612</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.1939703894627932</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.214624140535691</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.2193739831441971</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Sharpe Ratio</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1.144890112258371</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1.160894442697566</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1.080989801407628</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1.132898509608024</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1.126472658581236</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Information Ratio</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="n">
-        <v>0.8936043986040845</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.414883048441232</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.5996862667152726</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.5399633801994974</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>Maximum Drawdown</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>-0.2028774012753196</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-0.4525305106667451</v>
-      </c>
-      <c r="D5" t="n">
-        <v>-0.2715310900557988</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-0.2984331714520753</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-0.2753185598698785</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Annualized Volatility</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.1493704047926943</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.3487981709570898</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.1794377608467828</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.1894469263711449</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.1947441701962772</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>Value at Risk (95%)</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>-0.05269718626937447</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-0.1272865239573453</v>
-      </c>
-      <c r="D7" t="n">
-        <v>-0.0628198079366271</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-0.07467974982778716</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-0.08837081905292817</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Annualized Turnover</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C8" t="n">
-        <v>0.710015972005132</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.08432804632459089</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.1561427992380214</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.3434836760998189</v>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2">
+        <v>0.1710127068086176</v>
+      </c>
+      <c r="C2">
+        <v>0.40491763131112141</v>
+      </c>
+      <c r="D2">
+        <v>0.19397031690571731</v>
+      </c>
+      <c r="E2">
+        <v>0.21462403597024021</v>
+      </c>
+      <c r="F2">
+        <v>0.2193739173230366</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3">
+        <v>1.144890106066011</v>
+      </c>
+      <c r="C3">
+        <v>1.160894221197998</v>
+      </c>
+      <c r="D3">
+        <v>1.0809894832478051</v>
+      </c>
+      <c r="E3">
+        <v>1.132898253393066</v>
+      </c>
+      <c r="F3">
+        <v>1.126472416798336</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>0.89360370913474785</v>
+      </c>
+      <c r="D4">
+        <v>0.41488152368761311</v>
+      </c>
+      <c r="E4">
+        <v>0.59968487421369132</v>
+      </c>
+      <c r="F4">
+        <v>0.53996244941348448</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>-0.2028774385930536</v>
+      </c>
+      <c r="C5">
+        <v>-0.45253033533837911</v>
+      </c>
+      <c r="D5">
+        <v>-0.27153113665393358</v>
+      </c>
+      <c r="E5">
+        <v>-0.29843306300287797</v>
+      </c>
+      <c r="F5">
+        <v>-0.27531850993155088</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>0.1493704119745074</v>
+      </c>
+      <c r="C6">
+        <v>0.34879804198978781</v>
+      </c>
+      <c r="D6">
+        <v>0.1794377465384201</v>
+      </c>
+      <c r="E6">
+        <v>0.18944687691717629</v>
+      </c>
+      <c r="F6">
+        <v>0.19474415356440061</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>-5.2697183328736102E-2</v>
+      </c>
+      <c r="C7">
+        <v>-0.1272862655936598</v>
+      </c>
+      <c r="D7">
+        <v>-6.281976088033045E-2</v>
+      </c>
+      <c r="E7">
+        <v>-7.4679662390703921E-2</v>
+      </c>
+      <c r="F7">
+        <v>-8.8370681428955739E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0.71001540983625189</v>
+      </c>
+      <c r="D8">
+        <v>8.4328000536612532E-2</v>
+      </c>
+      <c r="E8">
+        <v>0.15614264306128409</v>
+      </c>
+      <c r="F8">
+        <v>0.34348362368572971</v>
       </c>
     </row>
   </sheetData>
